--- a/patent_analysis/did_region.xlsx
+++ b/patent_analysis/did_region.xlsx
@@ -3,13 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="15760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28780" windowHeight="13540" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="True" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="False" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region_东部" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region_中部" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region_西部" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -19,11 +23,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -369,12 +380,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -501,141 +527,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1243,7 +1272,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1256,7 +1285,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1302,22 +1331,22 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>-0.2964519894936588</v>
+        <v>-0.296451989493659</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.04959914695159104</v>
+        <v>0.049599146951591</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>-5.976957421928991</v>
+        <v>-5.97695742192899</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>2.324265668818271e-09</v>
+        <v>2.32426566881827e-09</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>-0.3936722707142302</v>
+        <v>-0.39367227071423</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>-0.1992317082730873</v>
+        <v>-0.199231708273087</v>
       </c>
     </row>
     <row r="3">
@@ -1327,22 +1356,22 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.1751255875828648</v>
+        <v>0.175125587582865</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.04830067113732291</v>
+        <v>0.0483006711373229</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>3.625738182497876</v>
+        <v>3.62573818249788</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.0002890786423235259</v>
+        <v>0.000289078642323526</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.08045047480933268</v>
+        <v>0.08045047480933271</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.2698007003563969</v>
+        <v>0.269800700356397</v>
       </c>
     </row>
     <row r="4">
@@ -1352,22 +1381,22 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.06322373207489904</v>
+        <v>0.06322373207489899</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.07312635628207832</v>
+        <v>0.07312635628207829</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.8645820096795086</v>
+        <v>0.864582009679509</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.3872818904986457</v>
+        <v>0.387281890498646</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>-0.0801127033141637</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.2065601674639618</v>
+        <v>0.206560167463962</v>
       </c>
     </row>
     <row r="5">
@@ -1377,22 +1406,22 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.0008151875379263846</v>
+        <v>0.000815187537926385</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.002780969857103858</v>
+        <v>0.00278096985710386</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.2931306629750143</v>
+        <v>0.293130662975014</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.7694262805622214</v>
+        <v>0.769426280562221</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>-0.00463584717114731</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.006266222247000078</v>
+        <v>0.00626622224700008</v>
       </c>
     </row>
     <row r="6">
@@ -1402,22 +1431,22 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.1129896311095499</v>
+        <v>0.11298963110955</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.06739377386504827</v>
+        <v>0.0673937738650483</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1.676558896016187</v>
+        <v>1.67655889601619</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.09364932876552667</v>
+        <v>0.0936493287655267</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>-0.01911025468224424</v>
+        <v>-0.0191102546822442</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.2450895169013441</v>
+        <v>0.245089516901344</v>
       </c>
     </row>
     <row r="7">
@@ -1427,22 +1456,22 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.4230960731263804</v>
+        <v>0.42309607312638</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.05364335643292915</v>
+        <v>0.0536433564329291</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>7.887203584201184</v>
+        <v>7.88720358420118</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>3.33066907387547e-15</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.3179486559114271</v>
+        <v>0.317948655911427</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.5282434903413338</v>
+        <v>0.528243490341334</v>
       </c>
     </row>
     <row r="8">
@@ -1452,22 +1481,22 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.2341009115198564</v>
+        <v>0.234100911519856</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.04487651884377569</v>
+        <v>0.0448765188437757</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>5.21655684423316</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>1.846727568644013e-07</v>
+        <v>1.84672756864401e-07</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>0.146137548229549</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.3220642748101638</v>
+        <v>0.322064274810164</v>
       </c>
     </row>
     <row r="9">
@@ -1477,22 +1506,22 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>-0.2000451505599114</v>
+        <v>-0.200045150559911</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.04951431526563905</v>
+        <v>0.049514315265639</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>-4.040147773157932</v>
+        <v>-4.04014777315793</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>5.368010652695432e-05</v>
+        <v>5.36801065269543e-05</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>-0.2970991514939949</v>
+        <v>-0.297099151493995</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>-0.1029911496258279</v>
+        <v>-0.102991149625828</v>
       </c>
     </row>
   </sheetData>
@@ -1507,40 +1536,291 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.17288135769885</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.06713723596410121</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-2.57504431358019</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.010032645155315</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.304479020380176</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.0412836950175249</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.129350543020783</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.07413573772924251</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>1.74477987247116</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.0810445977177745</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.0159650879584358</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.274666174000002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>-0.096260837397906</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.0842239673470155</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>-1.14291502086689</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.253092940122948</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.261350702737939</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.0688290279421275</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0.00424262254864979</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.00327709307467303</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1.29462986005459</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.195468774561146</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.00218090357397351</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.0106661486712731</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.16820576535669</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.0747412407854704</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2.25050806742011</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.0244317883541136</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.0217032701016081</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.314708260611772</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>投资阶段_成熟期</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.437969882255264</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.06299295623445771</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>6.95268024293311</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>3.7390091023326e-12</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0.314495543659105</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.561444220851423</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>投资阶段_扩张期</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0.125641350228542</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0.0513864891257929</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>2.44502693929867</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0.0144960698452528</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0.0249171877686874</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0.226365512688396</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>投资阶段_种子期</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>-0.30198449962948</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>0.0585234555394728</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>-5.16005927616146</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>2.50163873172227e-07</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>-0.416698039000495</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>-0.187270960258464</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>系数</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>标准误</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>t值</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>p值</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>置信区间下限</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>置信区间上限</t>
         </is>
@@ -1553,22 +1833,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1728813576988504</v>
+        <v>0.2228721147559267</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06713723596410119</v>
+        <v>0.3341140462746699</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.575044313580193</v>
+        <v>0.6670540111705063</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01003264515531499</v>
+        <v>0.5051382578517731</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3044790203801759</v>
+        <v>-0.4340498794532164</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.04128369501752485</v>
+        <v>0.8797941089650698</v>
       </c>
     </row>
     <row r="3">
@@ -1578,22 +1858,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1293505430207831</v>
+        <v>-0.429714066824716</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07413573772924248</v>
+        <v>0.2756394882962252</v>
       </c>
       <c r="D3" t="n">
-        <v>1.74477987247116</v>
+        <v>-1.558971355957929</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0810445977177745</v>
+        <v>0.1198269043850761</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01596508795843579</v>
+        <v>-0.9716656679420368</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2746661740000019</v>
+        <v>0.1122375342926049</v>
       </c>
     </row>
     <row r="4">
@@ -1603,22 +1883,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09626083739790602</v>
+        <v>0.4077631012678804</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08422396734701547</v>
+        <v>0.845224154295135</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.142915020866885</v>
+        <v>0.4824319077912885</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2530929401229476</v>
+        <v>0.6297740401253558</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2613507027379395</v>
+        <v>-1.254083633953892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06882902794212746</v>
+        <v>2.069609836489653</v>
       </c>
     </row>
     <row r="5">
@@ -1628,22 +1908,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004242622548649793</v>
+        <v>-0.0112987271213481</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003277093074673026</v>
+        <v>0.05697143638852914</v>
       </c>
       <c r="D5" t="n">
-        <v>1.294629860054586</v>
+        <v>-0.1983226654896669</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1954687745611463</v>
+        <v>0.842897570901133</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002180903573973512</v>
+        <v>-0.1233137412238823</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0106661486712731</v>
+        <v>0.1007162869811861</v>
       </c>
     </row>
     <row r="6">
@@ -1653,97 +1933,550 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1682057653566902</v>
+        <v>-0.7235771697373953</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0747412407854704</v>
+        <v>0.3244176866035041</v>
       </c>
       <c r="D6" t="n">
-        <v>2.250508067420112</v>
+        <v>-2.230387551655699</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02443178835411364</v>
+        <v>0.02629892826533187</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02170327010160811</v>
+        <v>-1.361434560100117</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3147082606117724</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>投资阶段_成熟期</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.4379698822552637</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.06299295623445765</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6.952680242933108</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.739009102332602e-12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.3144955436591046</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.5614442208514228</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>投资阶段_扩张期</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.1256413502285416</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.05138648912579288</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.445026939298666</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.01449606984525276</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.02491718776868737</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.2263655126883957</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>投资阶段_种子期</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.3019844996294796</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.05852345553947279</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-5.160059276161465</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.501638731722267e-07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.4166980390004953</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.1872709602584639</v>
+        <v>-0.08571977937467312</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.05306521089965539</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.04628844956748045</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-1.146402858499194</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.2516396389784235</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.1437933640442713</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.03766294224496049</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.1452033341831986</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.04902016335489363</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>2.962114449353485</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.003058259204781866</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.04912085724576769</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.2412858111206296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.1491019183855673</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.06770427075169411</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>2.202252778593535</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.02765669110219493</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0.01639746397628142</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.2818063727948532</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0.0008280362881086052</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.00287352879971618</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0.2881600797564273</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.7732266300090258</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.004804253482713041</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.006460326058930252</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>-0.03309739362317568</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.05885043584525777</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>-0.5623984452757915</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.5738496970451274</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.1484477975768022</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.08225301033045083</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.3633265008597569</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.08884982427455049</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-4.089220252558514</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>4.400687357586364e-05</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.5375138615411315</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.1891391401783824</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.1686702296569787</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.08153919324328057</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>2.068578593287448</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.03864026859824876</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.00881513732446812</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.3285253219894894</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>-0.461098737562626</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.2483360560478189</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>-1.85675308249978</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.06340888262881239</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.9479539735541473</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.02575649842889532</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0.009172568055639645</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.01166664415994739</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0.7862216357922248</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.4317773317023923</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01369953068875924</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.03204466680003853</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.5155702302020797</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.1441490908311396</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>3.57664572998267</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.000351538380682026</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.2329703502191097</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.7981701101850497</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.3817977660419791</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.08724393840389995</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-4.376209660256604</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>1.244848865100678e-05</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.5528551800242167</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.2107403520597414</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.1968355152682529</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.07356185543156324</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>2.675782361843425</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.007492159173045465</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.05260428284035115</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.3410667476961545</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>-0.5127224499304451</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.2118762233084057</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>-2.419914995294822</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.01557756575737912</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.9281438477549027</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>-0.09730105210598766</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-8.860269558530221e-05</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.005724405792558586</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-0.01547805987138104</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.9876517192293794</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01131232859991978</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.01113512320874917</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.6924218068310695</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.2046777402816723</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>3.382985398794105</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.0007253406796550177</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.2911143281358405</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>1.093729285526298</v>
       </c>
     </row>
   </sheetData>
